--- a/data/Holdings/ANSP_priority_list.xlsx
+++ b/data/Holdings/ANSP_priority_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/Holdings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ABDD0A2-669E-CE40-BC20-774ED3AE9FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA871F8-573F-5241-80FB-E8F77BE09FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2060" yWindow="1240" windowWidth="25240" windowHeight="12800" xr2:uid="{E09C4BC0-6DC9-8445-9F98-ADADBB01CEC8}"/>
   </bookViews>
